--- a/rcads/data/xls/03p_ActivityPersonRoles.xlsx
+++ b/rcads/data/xls/03p_ActivityPersonRoles.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_03p_ActivityPersonRoles"/>
   </sheets>
   <definedNames>
-    <definedName name="_03p_ActivityPersonRoles">'_03p_ActivityPersonRoles'!$A$1:$D$200</definedName>
+    <definedName name="_03p_ActivityPersonRoles">'_03p_ActivityPersonRoles'!$A$1:$D$230</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -3154,6 +3154,426 @@
         <v>1</v>
       </c>
     </row>
+    <row outlineLevel="0" r="201">
+      <c r="A201" s="0">
+        <v>223</v>
+      </c>
+      <c r="B201" s="0">
+        <v>121</v>
+      </c>
+      <c r="C201" s="0">
+        <v>108</v>
+      </c>
+      <c r="D201" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="202">
+      <c r="A202" s="0">
+        <v>224</v>
+      </c>
+      <c r="B202" s="0">
+        <v>122</v>
+      </c>
+      <c r="C202" s="0">
+        <v>108</v>
+      </c>
+      <c r="D202" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="203">
+      <c r="A203" s="0">
+        <v>225</v>
+      </c>
+      <c r="B203" s="0">
+        <v>124</v>
+      </c>
+      <c r="C203" s="0">
+        <v>113</v>
+      </c>
+      <c r="D203" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="204">
+      <c r="A204" s="0">
+        <v>226</v>
+      </c>
+      <c r="B204" s="0">
+        <v>124</v>
+      </c>
+      <c r="C204" s="0">
+        <v>114</v>
+      </c>
+      <c r="D204" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="205">
+      <c r="A205" s="0">
+        <v>227</v>
+      </c>
+      <c r="B205" s="0">
+        <v>124</v>
+      </c>
+      <c r="C205" s="0">
+        <v>115</v>
+      </c>
+      <c r="D205" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="206">
+      <c r="A206" s="0">
+        <v>228</v>
+      </c>
+      <c r="B206" s="0">
+        <v>123</v>
+      </c>
+      <c r="C206" s="0">
+        <v>113</v>
+      </c>
+      <c r="D206" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="207">
+      <c r="A207" s="0">
+        <v>229</v>
+      </c>
+      <c r="B207" s="0">
+        <v>123</v>
+      </c>
+      <c r="C207" s="0">
+        <v>114</v>
+      </c>
+      <c r="D207" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="208">
+      <c r="A208" s="0">
+        <v>230</v>
+      </c>
+      <c r="B208" s="0">
+        <v>123</v>
+      </c>
+      <c r="C208" s="0">
+        <v>115</v>
+      </c>
+      <c r="D208" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="209">
+      <c r="A209" s="0">
+        <v>231</v>
+      </c>
+      <c r="B209" s="0">
+        <v>125</v>
+      </c>
+      <c r="C209" s="0">
+        <v>116</v>
+      </c>
+      <c r="D209" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="210">
+      <c r="A210" s="0">
+        <v>232</v>
+      </c>
+      <c r="B210" s="0">
+        <v>125</v>
+      </c>
+      <c r="C210" s="0">
+        <v>117</v>
+      </c>
+      <c r="D210" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="211">
+      <c r="A211" s="0">
+        <v>233</v>
+      </c>
+      <c r="B211" s="0">
+        <v>126</v>
+      </c>
+      <c r="C211" s="0">
+        <v>116</v>
+      </c>
+      <c r="D211" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="212">
+      <c r="A212" s="0">
+        <v>234</v>
+      </c>
+      <c r="B212" s="0">
+        <v>126</v>
+      </c>
+      <c r="C212" s="0">
+        <v>117</v>
+      </c>
+      <c r="D212" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="213">
+      <c r="A213" s="0">
+        <v>235</v>
+      </c>
+      <c r="B213" s="0">
+        <v>127</v>
+      </c>
+      <c r="C213" s="0">
+        <v>118</v>
+      </c>
+      <c r="D213" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="214">
+      <c r="A214" s="0">
+        <v>236</v>
+      </c>
+      <c r="B214" s="0">
+        <v>127</v>
+      </c>
+      <c r="C214" s="0">
+        <v>118</v>
+      </c>
+      <c r="D214" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="215">
+      <c r="A215" s="0">
+        <v>237</v>
+      </c>
+      <c r="B215" s="0">
+        <v>127</v>
+      </c>
+      <c r="C215" s="0">
+        <v>119</v>
+      </c>
+      <c r="D215" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="216">
+      <c r="A216" s="0">
+        <v>238</v>
+      </c>
+      <c r="B216" s="0">
+        <v>127</v>
+      </c>
+      <c r="C216" s="0">
+        <v>119</v>
+      </c>
+      <c r="D216" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="217">
+      <c r="A217" s="0">
+        <v>239</v>
+      </c>
+      <c r="B217" s="0">
+        <v>127</v>
+      </c>
+      <c r="C217" s="0">
+        <v>120</v>
+      </c>
+      <c r="D217" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="218">
+      <c r="A218" s="0">
+        <v>240</v>
+      </c>
+      <c r="B218" s="0">
+        <v>127</v>
+      </c>
+      <c r="C218" s="0">
+        <v>121</v>
+      </c>
+      <c r="D218" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="219">
+      <c r="A219" s="0">
+        <v>241</v>
+      </c>
+      <c r="B219" s="0">
+        <v>127</v>
+      </c>
+      <c r="C219" s="0">
+        <v>121</v>
+      </c>
+      <c r="D219" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="220">
+      <c r="A220" s="0">
+        <v>242</v>
+      </c>
+      <c r="B220" s="0">
+        <v>128</v>
+      </c>
+      <c r="C220" s="0">
+        <v>118</v>
+      </c>
+      <c r="D220" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="221">
+      <c r="A221" s="0">
+        <v>243</v>
+      </c>
+      <c r="B221" s="0">
+        <v>128</v>
+      </c>
+      <c r="C221" s="0">
+        <v>118</v>
+      </c>
+      <c r="D221" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="222">
+      <c r="A222" s="0">
+        <v>244</v>
+      </c>
+      <c r="B222" s="0">
+        <v>128</v>
+      </c>
+      <c r="C222" s="0">
+        <v>119</v>
+      </c>
+      <c r="D222" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="223">
+      <c r="A223" s="0">
+        <v>245</v>
+      </c>
+      <c r="B223" s="0">
+        <v>128</v>
+      </c>
+      <c r="C223" s="0">
+        <v>119</v>
+      </c>
+      <c r="D223" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="224">
+      <c r="A224" s="0">
+        <v>246</v>
+      </c>
+      <c r="B224" s="0">
+        <v>128</v>
+      </c>
+      <c r="C224" s="0">
+        <v>120</v>
+      </c>
+      <c r="D224" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="225">
+      <c r="A225" s="0">
+        <v>247</v>
+      </c>
+      <c r="B225" s="0">
+        <v>128</v>
+      </c>
+      <c r="C225" s="0">
+        <v>121</v>
+      </c>
+      <c r="D225" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="226">
+      <c r="A226" s="0">
+        <v>248</v>
+      </c>
+      <c r="B226" s="0">
+        <v>128</v>
+      </c>
+      <c r="C226" s="0">
+        <v>121</v>
+      </c>
+      <c r="D226" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="227">
+      <c r="A227" s="0">
+        <v>249</v>
+      </c>
+      <c r="B227" s="0">
+        <v>129</v>
+      </c>
+      <c r="C227" s="0">
+        <v>108</v>
+      </c>
+      <c r="D227" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="228">
+      <c r="A228" s="0">
+        <v>250</v>
+      </c>
+      <c r="B228" s="0">
+        <v>130</v>
+      </c>
+      <c r="C228" s="0">
+        <v>108</v>
+      </c>
+      <c r="D228" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="229">
+      <c r="A229" s="0">
+        <v>251</v>
+      </c>
+      <c r="B229" s="0">
+        <v>131</v>
+      </c>
+      <c r="C229" s="0">
+        <v>108</v>
+      </c>
+      <c r="D229" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="230">
+      <c r="A230" s="0">
+        <v>252</v>
+      </c>
+      <c r="B230" s="0">
+        <v>132</v>
+      </c>
+      <c r="C230" s="0">
+        <v>108</v>
+      </c>
+      <c r="D230" s="0">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
